--- a/experiments.xlsx
+++ b/experiments.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6117c4724d8729c8/gabor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6117c4724d8729c8/gabor/Wavelet-Gabor-splat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="11_AD4DA82427541F7ACA7EB861484D34366BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72EBE22E-C363-47CE-A56A-7C591362B243}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="11_AD4DA82427541F7ACA7EB861484D34366BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{396C4937-935F-4C5B-B8B2-005C13A944B7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t>points</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,10 +120,6 @@
     <t>GaussianImage_Cholesky_50000_70000</t>
   </si>
   <si>
-    <t>F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GaussianImage_Cholesky_50000_70000_2_3000</t>
   </si>
   <si>
@@ -138,6 +134,64 @@
   </si>
   <si>
     <t>WIPESImage_Cholesky_50000_70000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_2_4000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>new gabor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_1</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_4000_0.1_0.1</t>
+  </si>
+  <si>
+    <t>no learnable w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_0.1_0.1</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_0.01</t>
+  </si>
+  <si>
+    <t>bigger lr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_8_0.01</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_12_0.01</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_16_0.01</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_75000_70000_4000_24_0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_4000_32_0.01</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_5000_24_0.01</t>
+  </si>
+  <si>
+    <t>GaussianImage_Cholesky_50000_70000_24_0.01</t>
+  </si>
+  <si>
+    <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +224,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,6 +243,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -202,14 +262,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -494,47 +563,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46.58203125" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="4"/>
-    <col min="11" max="11" width="31.75" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" style="4"/>
-    <col min="19" max="19" width="33.5" customWidth="1"/>
+    <col min="10" max="10" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="3"/>
+    <col min="12" max="12" width="31.75" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3"/>
+    <col min="20" max="20" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="4"/>
+      <c r="L1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="S1" s="3" t="s">
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="T1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -562,47 +633,48 @@
       <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="2"/>
+      <c r="L2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="N2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="V2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -630,44 +702,44 @@
       <c r="I3">
         <v>0.464277</v>
       </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3">
-        <v>70000</v>
+      <c r="L3" t="s">
+        <v>31</v>
       </c>
       <c r="M3">
+        <v>70000</v>
+      </c>
+      <c r="N3">
         <v>50000</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>44.9084</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.99938199999999999</v>
       </c>
-      <c r="Q3">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3">
+      <c r="R3">
+        <v>24</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3">
         <v>15000</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>10000</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>39.639200000000002</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>0.994834</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -695,26 +767,26 @@
       <c r="I4">
         <v>0.47277400000000003</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>25</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>15000</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>10000</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>31.152999999999999</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>0.98979899999999998</v>
       </c>
-      <c r="X4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -742,26 +814,26 @@
       <c r="I5">
         <v>0.47433700000000001</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>26</v>
       </c>
-      <c r="T5">
-        <v>70000</v>
-      </c>
       <c r="U5">
+        <v>70000</v>
+      </c>
+      <c r="V5">
         <v>50000</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>43.144500000000001</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>0.99921800000000005</v>
       </c>
-      <c r="X5">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -790,7 +862,7 @@
         <v>0.46014899999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -819,7 +891,7 @@
         <v>0.75722500000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -848,7 +920,7 @@
         <v>0.82969800000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -877,7 +949,7 @@
         <v>0.798786</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -906,7 +978,7 @@
         <v>0.858545</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -935,7 +1007,7 @@
         <v>0.85468200000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -964,7 +1036,7 @@
         <v>0.84781899999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -993,7 +1065,7 @@
         <v>0.86509100000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1022,9 +1094,9 @@
         <v>0.87426999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>24</v>
@@ -1049,9 +1121,9 @@
         <v>0.99919999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -1076,9 +1148,9 @@
         <v>0.99919999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>24</v>
@@ -1103,9 +1175,9 @@
         <v>0.99909999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>24</v>
@@ -1130,54 +1202,465 @@
         <v>0.99729999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20">
-        <v>24</v>
-      </c>
-      <c r="C20">
-        <v>70000</v>
-      </c>
-      <c r="D20">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>70000</v>
+      </c>
+      <c r="D19">
+        <v>100000</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>24</v>
+      </c>
+      <c r="C23">
+        <v>70000</v>
+      </c>
+      <c r="D23">
         <v>50000</v>
       </c>
-      <c r="E20">
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>45.289200000000001</v>
+      </c>
+      <c r="I23">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>24</v>
+      </c>
+      <c r="C24">
+        <v>70000</v>
+      </c>
+      <c r="D24">
+        <v>50000</v>
+      </c>
+      <c r="E24">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H24">
+        <v>43.623600000000003</v>
+      </c>
+      <c r="I24">
+        <v>0.999</v>
+      </c>
+      <c r="J24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>70000</v>
+      </c>
+      <c r="D25">
+        <v>75000</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="H25">
+        <v>41.841000000000001</v>
+      </c>
+      <c r="I25">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>24</v>
+      </c>
+      <c r="C26">
+        <v>70000</v>
+      </c>
+      <c r="D26">
+        <v>50000</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" s="1">
         <v>1E-3</v>
       </c>
-      <c r="G20">
-        <v>3000</v>
-      </c>
-      <c r="H20">
-        <v>36.107399999999998</v>
-      </c>
-      <c r="I20">
-        <v>0.99239999999999995</v>
+      <c r="H26">
+        <v>43.623600000000003</v>
+      </c>
+      <c r="I26">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27">
+        <v>70000</v>
+      </c>
+      <c r="D27">
+        <v>75000</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H27">
+        <v>46.014899999999997</v>
+      </c>
+      <c r="I27">
+        <v>0.99960000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28">
+        <v>24</v>
+      </c>
+      <c r="C28">
+        <v>70000</v>
+      </c>
+      <c r="D28">
+        <v>75000</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H28">
+        <v>47.797800000000002</v>
+      </c>
+      <c r="I28">
+        <v>0.99960000000000004</v>
+      </c>
+      <c r="J28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>24</v>
+      </c>
+      <c r="C29">
+        <v>70000</v>
+      </c>
+      <c r="D29">
+        <v>75000</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H29">
+        <v>48.572499999999998</v>
+      </c>
+      <c r="I29">
+        <v>0.99960000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>70000</v>
+      </c>
+      <c r="D30">
+        <v>75000</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H30">
+        <v>49.399799999999999</v>
+      </c>
+      <c r="I30">
+        <v>0.99970000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31">
+        <v>70000</v>
+      </c>
+      <c r="D31">
+        <v>75000</v>
+      </c>
+      <c r="E31">
+        <v>12</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H31">
+        <v>49.6477</v>
+      </c>
+      <c r="I31">
+        <v>0.99970000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>24</v>
+      </c>
+      <c r="C32">
+        <v>70000</v>
+      </c>
+      <c r="D32">
+        <v>75000</v>
+      </c>
+      <c r="E32">
+        <v>16</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H32">
+        <v>49.862900000000003</v>
+      </c>
+      <c r="I32">
+        <v>0.99970000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>24</v>
+      </c>
+      <c r="C33">
+        <v>70000</v>
+      </c>
+      <c r="D33">
+        <v>75000</v>
+      </c>
+      <c r="E33">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H33">
+        <v>50.037399999999998</v>
+      </c>
+      <c r="I33">
+        <v>0.99980000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>24</v>
+      </c>
+      <c r="C34">
+        <v>70000</v>
+      </c>
+      <c r="D34">
+        <v>75000</v>
+      </c>
+      <c r="E34">
+        <v>32</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="H34">
+        <v>48.441899999999997</v>
+      </c>
+      <c r="I34">
+        <v>0.99960000000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>24</v>
+      </c>
+      <c r="C35">
+        <v>70000</v>
+      </c>
+      <c r="D35">
+        <v>50000</v>
+      </c>
+      <c r="E35">
+        <v>24</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G35">
+        <v>5000</v>
+      </c>
+      <c r="H35">
+        <v>48.435099999999998</v>
+      </c>
+      <c r="I35">
+        <v>0.99960000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36">
+        <v>24</v>
+      </c>
+      <c r="C36">
+        <v>70000</v>
+      </c>
+      <c r="D36">
+        <v>50000</v>
+      </c>
+      <c r="E36">
+        <v>24</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36">
+        <v>45.586599999999997</v>
+      </c>
+      <c r="I36">
+        <v>0.99970000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F37" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F38" s="1">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="S1:W1"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="L1:R1"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
